--- a/experiment/SwinT2_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/SwinT2_bestx4/Test/results-B100/B100.xlsx
@@ -455,7 +455,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5695</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.62</v>
+        <v>28.64</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8106</v>
+        <v>0.8111</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.49</v>
+        <v>26.53</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8107</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.59</v>
+        <v>30.62</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8478</v>
+        <v>0.8485</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>26.24</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7091</v>
+        <v>0.7094</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.82</v>
+        <v>33.84</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8922</v>
+        <v>0.8921</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>26.3</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7488</v>
+        <v>0.7492</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>23.11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5921</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.47</v>
+        <v>27.48</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7865</v>
+        <v>0.7869</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.29</v>
+        <v>29.3</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8021</v>
+        <v>0.8024</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.43</v>
+        <v>24.46</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7244</v>
+        <v>0.7261</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.99</v>
+        <v>28.01</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7499</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.02</v>
+        <v>30.03</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8077</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.34</v>
+        <v>29.37</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8286</v>
+        <v>0.8296</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.05</v>
+        <v>25.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6785</v>
+        <v>0.6792</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.82</v>
+        <v>24.85</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7558</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.67</v>
+        <v>34.71</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8918</v>
+        <v>0.8922</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>32.89</v>
+        <v>32.93</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8919</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.15</v>
+        <v>26.17</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7351</v>
+        <v>0.736</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>26.08</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8005</v>
+        <v>0.8007</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.04</v>
+        <v>22.01</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6763</v>
+        <v>0.6748</v>
       </c>
     </row>
     <row r="23">
@@ -728,7 +728,7 @@
         <v>23.78</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6241</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.83</v>
+        <v>24.84</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5725</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.53</v>
+        <v>26.5</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.6</v>
+        <v>27.63</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8193</v>
+        <v>0.8201000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26.95</v>
+        <v>26.97</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8355</v>
+        <v>0.8362000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>27.68</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7342</v>
+        <v>0.734</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         <v>29.53</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8001</v>
+        <v>0.8004</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.31</v>
+        <v>32.36</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9008</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.89</v>
+        <v>19.9</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5036</v>
+        <v>0.5044</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.74</v>
+        <v>29.75</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8159</v>
+        <v>0.8163</v>
       </c>
     </row>
     <row r="33">
@@ -858,7 +858,7 @@
         <v>20.93</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4262</v>
+        <v>0.4265</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.17</v>
+        <v>25.18</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6696</v>
+        <v>0.6702</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.36</v>
+        <v>24.38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7519</v>
+        <v>0.7524999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.56</v>
+        <v>34.68</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8891</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7371</v>
+        <v>0.7374000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.2</v>
+        <v>28.21</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7158</v>
+        <v>0.7161999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.47</v>
+        <v>28.48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7432</v>
+        <v>0.7435</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.17</v>
+        <v>35.28</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9478</v>
+        <v>0.9491000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
+        <v>26.99</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7477</v>
+        <v>0.7478</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         <v>25.8</v>
       </c>
       <c r="C43" t="n">
-        <v>0.719</v>
+        <v>0.7193000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.67</v>
+        <v>26.66</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7581</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27.91</v>
+        <v>27.94</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8729</v>
+        <v>0.8732</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.75</v>
+        <v>24.78</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6754</v>
+        <v>0.6778</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.52</v>
+        <v>34.58</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8688</v>
+        <v>0.8699</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.76</v>
+        <v>22.77</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6206</v>
+        <v>0.6209</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.94</v>
+        <v>24.95</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6317</v>
+        <v>0.6323</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.24</v>
+        <v>27.26</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8712</v>
+        <v>0.8727</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.19</v>
+        <v>32.2</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8401</v>
+        <v>0.8404</v>
       </c>
     </row>
     <row r="52">
@@ -1105,7 +1105,7 @@
         <v>24.81</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6172</v>
+        <v>0.6173</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         <v>22.59</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7033</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.27</v>
+        <v>32.32</v>
       </c>
       <c r="C54" t="n">
-        <v>0.842</v>
+        <v>0.8429</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.51</v>
+        <v>32.49</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7984</v>
+        <v>0.7981</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.63</v>
+        <v>27.65</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7729</v>
+        <v>0.7737000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.57</v>
+        <v>25.58</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6935</v>
+        <v>0.6941000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -1196,7 +1196,7 @@
         <v>27.46</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7257</v>
+        <v>0.7264</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.01</v>
+        <v>32.02</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7919</v>
+        <v>0.7921</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>31.19</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7841</v>
+        <v>0.7844</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.7</v>
+        <v>31.71</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8142</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.93</v>
+        <v>28.97</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7932</v>
+        <v>0.7938</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.42</v>
+        <v>33.66</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9505</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.29</v>
+        <v>24.3</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6691</v>
+        <v>0.6701</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26</v>
+        <v>26.01</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6201</v>
+        <v>0.6204</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.33</v>
+        <v>28.35</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7932</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.54</v>
+        <v>39.6</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9797</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.94</v>
+        <v>20.97</v>
       </c>
       <c r="C69" t="n">
-        <v>0.571</v>
+        <v>0.5728</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.79</v>
+        <v>22.81</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6492</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.8</v>
+        <v>28.83</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8072</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.3</v>
+        <v>30.36</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8125</v>
+        <v>0.8138</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>25.46</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5959</v>
+        <v>0.5962</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.2</v>
+        <v>27.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6051</v>
+        <v>0.6054</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.26</v>
+        <v>26.27</v>
       </c>
       <c r="C75" t="n">
-        <v>0.695</v>
+        <v>0.6951000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>24.1</v>
       </c>
       <c r="C76" t="n">
-        <v>0.694</v>
+        <v>0.6939</v>
       </c>
     </row>
     <row r="77">
@@ -1443,7 +1443,7 @@
         <v>23.67</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4773</v>
+        <v>0.4775</v>
       </c>
     </row>
     <row r="79">
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.87</v>
+        <v>29.85</v>
       </c>
       <c r="C79" t="n">
         <v>0.8114</v>
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.43</v>
+        <v>32.53</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9502</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>29.76</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8185</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.75</v>
+        <v>35.77</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9382</v>
+        <v>0.9384</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.51</v>
+        <v>28.52</v>
       </c>
       <c r="C83" t="n">
-        <v>0.718</v>
+        <v>0.7184</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.25</v>
+        <v>22.26</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5286</v>
+        <v>0.5294</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>21.06</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.6034</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.6</v>
+        <v>25.66</v>
       </c>
       <c r="C86" t="n">
-        <v>0.785</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>25.01</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5999</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.33</v>
+        <v>27.35</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6926</v>
+        <v>0.6936</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.63</v>
+        <v>30.66</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8113</v>
+        <v>0.8121</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.2</v>
+        <v>27.21</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5592</v>
+        <v>0.5596</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.08</v>
+        <v>25.1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6427</v>
+        <v>0.6443</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.03</v>
+        <v>29.05</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7117</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.33</v>
+        <v>26.35</v>
       </c>
       <c r="C93" t="n">
-        <v>0.743</v>
+        <v>0.7444</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.68</v>
+        <v>30.8</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8767</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>25.88</v>
+        <v>25.9</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7117</v>
+        <v>0.7127</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.78</v>
+        <v>25.82</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7897</v>
+        <v>0.7914</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.92</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3154</v>
+        <v>0.3164</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>27.02</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5618</v>
+        <v>0.5623</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.23</v>
+        <v>26.26</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7765</v>
+        <v>0.7774</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.88</v>
+        <v>26.89</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7328</v>
+        <v>0.7334000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25</v>
+        <v>25.05</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7244</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.49</v>
+        <v>27.51</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7337</v>
+        <v>0.7343</v>
       </c>
     </row>
   </sheetData>
